--- a/Section 4.3/D_metrics_vs_load_m0.001_PV75.0_gr1.5.xlsx
+++ b/Section 4.3/D_metrics_vs_load_m0.001_PV75.0_gr1.5.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Reworked_TEA\nj=1,bj0.0005\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07E62DE-6B23-42C0-96F6-600A7DC5D31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="2" r:id="rId3"/>
+    <sheet name="data" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
@@ -47,12 +53,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -68,20 +80,346 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="false"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="false"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="false"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="true"/>
     <col min="2" max="2" width="11.7109375" customWidth="true"/>
@@ -92,7 +430,7 @@
     <col min="7" max="7" width="11.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
@@ -115,305 +453,263 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
       <c r="A2" s="0">
-        <v>7.7999999999999998</v>
+        <v>6.5</v>
       </c>
       <c r="B2" s="0">
-        <v>18.529294829862938</v>
+        <v>12.301400374293021</v>
       </c>
       <c r="C2" s="0">
-        <v>68.770474113865816</v>
+        <v>44.309811331339354</v>
       </c>
       <c r="D2" s="0">
-        <v>4.1933883944582746</v>
+        <v>3.014564872875237</v>
       </c>
       <c r="E2" s="0">
-        <v>30.610583212478922</v>
+        <v>30.394011926482225</v>
       </c>
       <c r="F2" s="0">
-        <v>64.261824102239686</v>
+        <v>64.05511866460094</v>
       </c>
       <c r="G2" s="0">
-        <v>8.1929173575165031</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>8.1090003260467114</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
       <c r="A3" s="0">
         <v>8</v>
       </c>
       <c r="B3" s="0">
-        <v>23.165056003500858</v>
+        <v>22.536326911394895</v>
       </c>
       <c r="C3" s="0">
-        <v>82.295227130666092</v>
+        <v>73.189645898971108</v>
       </c>
       <c r="D3" s="0">
-        <v>6.3328370812691475</v>
+        <v>9.9927816857687084</v>
       </c>
       <c r="E3" s="0">
-        <v>30.842781797944696</v>
+        <v>30.906007990731492</v>
       </c>
       <c r="F3" s="0">
-        <v>64.228694781552733</v>
+        <v>64.22951047498583</v>
       </c>
       <c r="G3" s="0">
-        <v>8.0516099837374</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>7.7349359607580546</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
       <c r="A4" s="0">
         <v>10</v>
       </c>
       <c r="B4" s="0">
-        <v>23.019808882585384</v>
+        <v>22.554883414995984</v>
       </c>
       <c r="C4" s="0">
-        <v>80.018901976377791</v>
+        <v>71.500010039883193</v>
       </c>
       <c r="D4" s="0">
-        <v>6.7602472618970637</v>
+        <v>10.13924919796602</v>
       </c>
       <c r="E4" s="0">
-        <v>30.640343905650436</v>
+        <v>30.737044747028268</v>
       </c>
       <c r="F4" s="0">
-        <v>63.972007127514928</v>
+        <v>63.900681621538659</v>
       </c>
       <c r="G4" s="0">
-        <v>8.0547051856416942</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>7.7329475356618369</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="0">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B5" s="0">
-        <v>23.204078132468709</v>
+        <v>22.203881728891236</v>
       </c>
       <c r="C5" s="0">
-        <v>80.068859380893528</v>
+        <v>67.559863171052072</v>
       </c>
       <c r="D5" s="0">
-        <v>7.0721020826373797</v>
+        <v>11.102994158852191</v>
       </c>
       <c r="E5" s="0">
-        <v>30.561539717921931</v>
+        <v>30.160358542741232</v>
       </c>
       <c r="F5" s="0">
-        <v>63.91639101672186</v>
+        <v>63.909211851537187</v>
       </c>
       <c r="G5" s="0">
-        <v>8.0482168278525101</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>7.7335652415232357</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
       <c r="A6" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B6" s="0">
-        <v>22.872073833500252</v>
+        <v>22.356990031987493</v>
       </c>
       <c r="C6" s="0">
-        <v>77.174633597514415</v>
+        <v>67.828058377437259</v>
       </c>
       <c r="D6" s="0">
-        <v>7.2910267254283472</v>
+        <v>11.516125538168344</v>
       </c>
       <c r="E6" s="0">
-        <v>30.350342665128373</v>
+        <v>29.35709443533533</v>
       </c>
       <c r="F6" s="0">
-        <v>63.794068180197613</v>
+        <v>63.6633060172867</v>
       </c>
       <c r="G6" s="0">
-        <v>8.0550011313965868</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>7.7167862329271584</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
       <c r="A7" s="0">
-        <v>15</v>
-      </c>
-      <c r="B7" s="0">
-        <v>22.883340017102125</v>
-      </c>
-      <c r="C7" s="0">
-        <v>77.274794597539454</v>
-      </c>
-      <c r="D7" s="0">
-        <v>7.6784113847719269</v>
-      </c>
-      <c r="E7" s="0">
-        <v>30.064669787721567</v>
-      </c>
-      <c r="F7" s="0">
-        <v>63.693104266369012</v>
-      </c>
-      <c r="G7" s="0">
-        <v>8.0506442693322278</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1">
+        <v>21.584813908580632</v>
+      </c>
+      <c r="C7" s="1">
+        <v>65.426619954873701</v>
+      </c>
+      <c r="D7" s="1">
+        <v>11.974330123975333</v>
+      </c>
+      <c r="E7" s="1">
+        <v>28.468994610927155</v>
+      </c>
+      <c r="F7" s="1">
+        <v>63.466805095005761</v>
+      </c>
+      <c r="G7" s="1">
+        <v>7.7225147277268427</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
       <c r="A8" s="0">
-        <v>18</v>
+        <v>28.000000000000004</v>
       </c>
       <c r="B8" s="0">
-        <v>22.834053246140996</v>
+        <v>21.438355257650091</v>
       </c>
       <c r="C8" s="0">
-        <v>77.584684361240676</v>
+        <v>65.91556316788612</v>
       </c>
       <c r="D8" s="0">
-        <v>8.140129234893017</v>
+        <v>11.854014083006675</v>
       </c>
       <c r="E8" s="0">
-        <v>29.6054760474765</v>
+        <v>27.860357080099302</v>
       </c>
       <c r="F8" s="0">
-        <v>63.588573514838217</v>
+        <v>63.395720576273874</v>
       </c>
       <c r="G8" s="0">
-        <v>8.0449235652898636</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>7.7146968247774312</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
       <c r="A9" s="0">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B9" s="0">
-        <v>22.592129984347583</v>
+        <v>20.947390999954642</v>
       </c>
       <c r="C9" s="0">
-        <v>76.175184172675642</v>
+        <v>65.215934505269431</v>
       </c>
       <c r="D9" s="0">
-        <v>8.3468664470642775</v>
+        <v>11.816241962283023</v>
       </c>
       <c r="E9" s="0">
-        <v>29.244966641093392</v>
+        <v>27.445157613343842</v>
       </c>
       <c r="F9" s="0">
-        <v>63.557142600257237</v>
+        <v>63.28962965063409</v>
       </c>
       <c r="G9" s="0">
-        <v>8.0448930868327544</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>7.721161493558502</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
       <c r="A10" s="0">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B10" s="0">
-        <v>22.43845792614292</v>
+        <v>19.35016571134776</v>
       </c>
       <c r="C10" s="0">
-        <v>76.313537649714462</v>
+        <v>62.82679290571182</v>
       </c>
       <c r="D10" s="0">
-        <v>8.4903263552780519</v>
+        <v>9.3493699675448259</v>
       </c>
       <c r="E10" s="0">
-        <v>28.900410326945881</v>
+        <v>25.945984179736406</v>
       </c>
       <c r="F10" s="0">
-        <v>63.487199347237485</v>
+        <v>63.21484667438385</v>
       </c>
       <c r="G10" s="0">
-        <v>8.0433487275315585</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>7.7375500000304607</v>
+      </c>
+      <c r="Q10">
+        <v>21.584813908580632</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
       <c r="A11" s="0">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B11" s="0">
-        <v>21.874927184041088</v>
+        <v>17.697471857307271</v>
       </c>
       <c r="C11" s="0">
-        <v>75.608338495520726</v>
+        <v>61.481634423386851</v>
       </c>
       <c r="D11" s="0">
-        <v>8.4225458541956186</v>
+        <v>10.400979178210601</v>
       </c>
       <c r="E11" s="0">
-        <v>28.403171290854065</v>
+        <v>23.977346232878968</v>
       </c>
       <c r="F11" s="0">
-        <v>63.325847024292223</v>
+        <v>63.139434351018103</v>
       </c>
       <c r="G11" s="0">
-        <v>8.0506093413674673</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0">
-        <v>28.000000000000004</v>
-      </c>
-      <c r="B12" s="0">
-        <v>21.278385074628801</v>
-      </c>
-      <c r="C12" s="0">
-        <v>75.004644626051814</v>
-      </c>
-      <c r="D12" s="0">
-        <v>8.1922611847184132</v>
-      </c>
-      <c r="E12" s="0">
-        <v>27.809107144737254</v>
-      </c>
-      <c r="F12" s="0">
-        <v>63.252376945048518</v>
-      </c>
-      <c r="G12" s="0">
-        <v>8.0558100181737107</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0">
-        <v>30</v>
-      </c>
-      <c r="B13" s="0">
-        <v>21.007430712677273</v>
-      </c>
-      <c r="C13" s="0">
-        <v>74.808417552211893</v>
-      </c>
-      <c r="D13" s="0">
-        <v>7.9997779112642107</v>
-      </c>
-      <c r="E13" s="0">
-        <v>27.445912443049963</v>
-      </c>
-      <c r="F13" s="0">
-        <v>63.323888918130194</v>
-      </c>
-      <c r="G13" s="0">
-        <v>8.055101467255545</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0">
-        <v>35</v>
-      </c>
-      <c r="B14" s="0">
-        <v>19.023665236042689</v>
-      </c>
-      <c r="C14" s="0">
-        <v>70.337515523444651</v>
-      </c>
-      <c r="D14" s="0">
-        <v>5.7205444996075858</v>
-      </c>
-      <c r="E14" s="0">
-        <v>25.982938411494825</v>
-      </c>
-      <c r="F14" s="0">
-        <v>63.442108887217223</v>
-      </c>
-      <c r="G14" s="0">
-        <v>8.085972335861662</v>
+        <v>7.7468155606622</v>
+      </c>
+      <c r="Q11">
+        <v>65.426619954873701</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+      <c r="Q12">
+        <v>11.974330123975333</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+      <c r="Q13">
+        <v>28.468994610927155</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+      <c r="Q14">
+        <v>63.466805095005761</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+      <c r="Q15">
+        <v>7.7225147277268427</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>